--- a/output/2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale. Produttore/system integrator dal 1997, ~30 dipendenti, &gt;870 clienti, &gt;4.800 progetti. Progetta/produce/installa sistemi di aspirazione polveri, cabine di verniciatura, trasporto pneumatico, filtri a maniche e cartuccia.</t>
+          <t>Verificato via sito ufficiale. Produttore/system integrator dal 1997, ~30 dipendenti, &gt;870 clienti, &gt;4.800 progetti. Progetta/produce/installa sistemi di aspirazione polveri, cabine di verniciatura, trasporto pneumatico, filtri a maniche e cartuccia. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,7 +578,6 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato via sito ufficiale e pagina Filtration Group locations. Distributore/partner tecnico B2B dal 1998 per sistemi di filtrazione aria industriale (Filtration Group). Email generica non reperita da fonte verificabile (non inventata). Referenti: Aleksandar Ćurčija (sales engineer, +385 1 3870630 / +385 9 52169105), Marko Semren (direttore, +385 1 6146105 / +385 9 95265558).</t>

--- a/output/2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
